--- a/public/sample_uploads/fund_formulas.xlsx
+++ b/public/sample_uploads/fund_formulas.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="47">
   <si>
     <t xml:space="preserve">Sequence</t>
   </si>
@@ -56,6 +56,9 @@
   </si>
   <si>
     <t xml:space="preserve">Metadata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cache</t>
   </si>
   <si>
     <t xml:space="preserve">Management Fees</t>
@@ -233,12 +236,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -439,7 +446,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultColWidth="8.6171875" defaultRowHeight="13.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.12"/>
@@ -489,40 +496,46 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="G2" s="3" t="s">
+        <v>18</v>
+      </c>
       <c r="H2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>15</v>
+        <v>20</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -530,31 +543,34 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -562,34 +578,37 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -597,31 +616,34 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>15</v>
+        <v>32</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -629,31 +651,34 @@
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>15</v>
+      <c r="J6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -661,34 +686,37 @@
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>36</v>
+        <v>17</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>15</v>
+        <v>39</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -696,34 +724,37 @@
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>15</v>
+        <v>42</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -731,31 +762,34 @@
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>15</v>
+        <v>45</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -763,34 +797,37 @@
         <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>15</v>
+        <v>46</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
